--- a/backend/data/financials_by_company/1D2.F.xlsx
+++ b/backend/data/financials_by_company/1D2.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,570 +657,621 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-350054500</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>313430000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1400218000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-1400218000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1374142000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>143487000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>17345447000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1086788000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-1230275000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-107067000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>173908000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>66841000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-323978500</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1374142000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>17935685000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>886460400</v>
-      </c>
-      <c r="S2" t="n">
-        <v>886460400</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-1374142000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-1374142000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1374142000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32072000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1406214000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1406214000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2031000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1404183000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>16260000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1402136000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-12930000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1415066000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>-107067000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>173908000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>66841000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>80673000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>590238000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>596128000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>411209000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>184919000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>670911000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>17345447000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>18016358000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>18016358000</v>
-      </c>
+        <v>7936000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>3523000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-165044500</v>
+        <v>-26802250</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>322895000</v>
+        <v>164106000</v>
       </c>
       <c r="E3" t="n">
-        <v>-660178000</v>
+        <v>-107209000</v>
       </c>
       <c r="F3" t="n">
-        <v>-660178000</v>
+        <v>-107209000</v>
       </c>
       <c r="G3" t="n">
-        <v>-630045000</v>
+        <v>-275579000</v>
       </c>
       <c r="H3" t="n">
-        <v>143970000</v>
+        <v>139584000</v>
       </c>
       <c r="I3" t="n">
-        <v>16364641000</v>
+        <v>12870105000</v>
       </c>
       <c r="J3" t="n">
-        <v>-337283000</v>
+        <v>56897000</v>
       </c>
       <c r="K3" t="n">
-        <v>-481253000</v>
+        <v>-82687000</v>
       </c>
       <c r="L3" t="n">
-        <v>-116620000</v>
+        <v>-145458000</v>
       </c>
       <c r="M3" t="n">
-        <v>179827000</v>
+        <v>177790000</v>
       </c>
       <c r="N3" t="n">
-        <v>63207000</v>
+        <v>32332000</v>
       </c>
       <c r="O3" t="n">
-        <v>-134911500</v>
+        <v>-195172250</v>
       </c>
       <c r="P3" t="n">
-        <v>-630045000</v>
+        <v>-275579000</v>
       </c>
       <c r="Q3" t="n">
-        <v>16961007000</v>
+        <v>13488381000</v>
       </c>
       <c r="R3" t="n">
-        <v>748228000</v>
+        <v>732460000</v>
       </c>
       <c r="S3" t="n">
-        <v>748228000</v>
+        <v>732460000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.84</v>
+        <v>-0.38</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.84</v>
+        <v>-0.38</v>
       </c>
       <c r="V3" t="n">
-        <v>-630045000</v>
+        <v>-275579000</v>
       </c>
       <c r="W3" t="n">
-        <v>-630045000</v>
+        <v>-275579000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-630045000</v>
+        <v>-275579000</v>
       </c>
       <c r="Z3" t="n">
-        <v>35980000</v>
+        <v>3566000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-666025000</v>
+        <v>-279145000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-666025000</v>
+        <v>-279145000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4945000</v>
+        <v>18668000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-661080000</v>
+        <v>-260477000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-60953000</v>
+        <v>-22698000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-667617000</v>
+        <v>-107310000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-41695000</v>
+        <v>-1603000</v>
       </c>
       <c r="AH3" t="n">
-        <v>709312000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>108913000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1350000</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>-116620000</v>
+        <v>-145458000</v>
       </c>
       <c r="AK3" t="n">
-        <v>179827000</v>
+        <v>177790000</v>
       </c>
       <c r="AL3" t="n">
-        <v>63207000</v>
+        <v>32332000</v>
       </c>
       <c r="AM3" t="n">
-        <v>184985000</v>
+        <v>19156000</v>
       </c>
       <c r="AN3" t="n">
-        <v>596366000</v>
+        <v>618276000</v>
       </c>
       <c r="AO3" t="n">
-        <v>600604000</v>
+        <v>622461000</v>
       </c>
       <c r="AP3" t="n">
-        <v>395605000</v>
+        <v>418065000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>204999000</v>
+        <v>204396000</v>
       </c>
       <c r="AR3" t="n">
-        <v>781351000</v>
+        <v>637432000</v>
       </c>
       <c r="AS3" t="n">
-        <v>16364641000</v>
+        <v>12870105000</v>
       </c>
       <c r="AT3" t="n">
-        <v>17145992000</v>
+        <v>13507537000</v>
       </c>
       <c r="AU3" t="n">
-        <v>17145992000</v>
+        <v>13507537000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-26802250</v>
+        <v>-165044500</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>164106000</v>
+        <v>322895000</v>
       </c>
       <c r="E4" t="n">
-        <v>-107209000</v>
+        <v>-660178000</v>
       </c>
       <c r="F4" t="n">
-        <v>-107209000</v>
+        <v>-660178000</v>
       </c>
       <c r="G4" t="n">
-        <v>-275579000</v>
+        <v>-630045000</v>
       </c>
       <c r="H4" t="n">
-        <v>139584000</v>
+        <v>143970000</v>
       </c>
       <c r="I4" t="n">
-        <v>12870105000</v>
+        <v>16364641000</v>
       </c>
       <c r="J4" t="n">
-        <v>56897000</v>
+        <v>-337283000</v>
       </c>
       <c r="K4" t="n">
-        <v>-82687000</v>
+        <v>-481253000</v>
       </c>
       <c r="L4" t="n">
-        <v>-145458000</v>
+        <v>-116620000</v>
       </c>
       <c r="M4" t="n">
-        <v>177790000</v>
+        <v>179827000</v>
       </c>
       <c r="N4" t="n">
-        <v>32332000</v>
+        <v>63207000</v>
       </c>
       <c r="O4" t="n">
-        <v>-195172250</v>
+        <v>-134911500</v>
       </c>
       <c r="P4" t="n">
-        <v>-275579000</v>
+        <v>-630045000</v>
       </c>
       <c r="Q4" t="n">
-        <v>13488381000</v>
+        <v>16961007000</v>
       </c>
       <c r="R4" t="n">
-        <v>732460000</v>
+        <v>748228000</v>
       </c>
       <c r="S4" t="n">
-        <v>732460000</v>
+        <v>748228000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.38</v>
+        <v>-0.84</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.38</v>
+        <v>-0.84</v>
       </c>
       <c r="V4" t="n">
-        <v>-275579000</v>
+        <v>-630045000</v>
       </c>
       <c r="W4" t="n">
-        <v>-275579000</v>
+        <v>-630045000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-275579000</v>
+        <v>-630045000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3566000</v>
+        <v>35980000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-279145000</v>
+        <v>-666025000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-279145000</v>
+        <v>-666025000</v>
       </c>
       <c r="AC4" t="n">
-        <v>18668000</v>
+        <v>4945000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-260477000</v>
+        <v>-661080000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-22698000</v>
+        <v>-60953000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-107310000</v>
+        <v>-667617000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1603000</v>
+        <v>-41695000</v>
       </c>
       <c r="AH4" t="n">
-        <v>108913000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1350000</v>
-      </c>
+        <v>709312000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-145458000</v>
+        <v>-116620000</v>
       </c>
       <c r="AK4" t="n">
-        <v>177790000</v>
+        <v>179827000</v>
       </c>
       <c r="AL4" t="n">
-        <v>32332000</v>
+        <v>63207000</v>
       </c>
       <c r="AM4" t="n">
-        <v>19156000</v>
+        <v>184985000</v>
       </c>
       <c r="AN4" t="n">
-        <v>618276000</v>
+        <v>596366000</v>
       </c>
       <c r="AO4" t="n">
-        <v>622461000</v>
+        <v>600604000</v>
       </c>
       <c r="AP4" t="n">
-        <v>418065000</v>
+        <v>395605000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>204396000</v>
+        <v>204999000</v>
       </c>
       <c r="AR4" t="n">
-        <v>637432000</v>
+        <v>781351000</v>
       </c>
       <c r="AS4" t="n">
-        <v>12870105000</v>
+        <v>16364641000</v>
       </c>
       <c r="AT4" t="n">
-        <v>13507537000</v>
+        <v>17145992000</v>
       </c>
       <c r="AU4" t="n">
-        <v>13507537000</v>
+        <v>17145992000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-233580213.304368</v>
+        <v>-350054500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.078959</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-578472000</v>
+        <v>313430000</v>
       </c>
       <c r="E5" t="n">
-        <v>-2907711000</v>
+        <v>-1400218000</v>
       </c>
       <c r="F5" t="n">
-        <v>-2958232000</v>
+        <v>-1400218000</v>
       </c>
       <c r="G5" t="n">
-        <v>-3567438000</v>
+        <v>-1374142000</v>
       </c>
       <c r="H5" t="n">
-        <v>184996000</v>
+        <v>143487000</v>
       </c>
       <c r="I5" t="n">
-        <v>9668142000</v>
+        <v>17345447000</v>
       </c>
       <c r="J5" t="n">
-        <v>-3486183000</v>
+        <v>-1086788000</v>
       </c>
       <c r="K5" t="n">
-        <v>-3671179000</v>
+        <v>-1230275000</v>
       </c>
       <c r="L5" t="n">
-        <v>-216540000</v>
+        <v>-107067000</v>
       </c>
       <c r="M5" t="n">
-        <v>234170000</v>
+        <v>173908000</v>
       </c>
       <c r="N5" t="n">
-        <v>17630000</v>
+        <v>66841000</v>
       </c>
       <c r="O5" t="n">
-        <v>-792265213.304368</v>
+        <v>-323978500</v>
       </c>
       <c r="P5" t="n">
-        <v>-3567438000</v>
+        <v>-1374142000</v>
       </c>
       <c r="Q5" t="n">
-        <v>11055340000</v>
+        <v>17935685000</v>
       </c>
       <c r="R5" t="n">
-        <v>732460000</v>
+        <v>886460400</v>
       </c>
       <c r="S5" t="n">
-        <v>732460000</v>
+        <v>886460400</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.87</v>
+        <v>-1.55</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.87</v>
+        <v>-1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>-3567438000</v>
+        <v>-1374142000</v>
       </c>
       <c r="W5" t="n">
-        <v>-3567438000</v>
+        <v>-1374142000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-3567438000</v>
+        <v>-1374142000</v>
       </c>
       <c r="Z5" t="n">
-        <v>29547000</v>
+        <v>32072000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3596985000</v>
+        <v>-1406214000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3596985000</v>
+        <v>-1406214000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-308364000</v>
+        <v>2031000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-3905349000</v>
+        <v>-1404183000</v>
       </c>
       <c r="AE5" t="n">
-        <v>79036000</v>
+        <v>16260000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2961454000</v>
+        <v>-1402136000</v>
       </c>
       <c r="AG5" t="n">
-        <v>7936000</v>
+        <v>-12930000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2899474000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3523000</v>
-      </c>
+        <v>1415066000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>-216540000</v>
+        <v>-107067000</v>
       </c>
       <c r="AK5" t="n">
-        <v>234170000</v>
+        <v>173908000</v>
       </c>
       <c r="AL5" t="n">
-        <v>17630000</v>
+        <v>66841000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-811410000</v>
+        <v>80673000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1387198000</v>
+        <v>590238000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1393945000</v>
+        <v>596128000</v>
       </c>
       <c r="AP5" t="n">
-        <v>508835000</v>
+        <v>411209000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>885110000</v>
+        <v>184919000</v>
       </c>
       <c r="AR5" t="n">
-        <v>575788000</v>
+        <v>670911000</v>
       </c>
       <c r="AS5" t="n">
-        <v>9668142000</v>
+        <v>17345447000</v>
       </c>
       <c r="AT5" t="n">
-        <v>10243930000</v>
+        <v>18016358000</v>
       </c>
       <c r="AU5" t="n">
-        <v>10243930000</v>
+        <v>18016358000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-290173750</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>53415000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1160695000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1160695000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1439555000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>134047000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16080235000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1107280000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1241327000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-143157000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>209951000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>66794000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-569033750</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1439555000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>16661638000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>886460400</v>
+      </c>
+      <c r="S6" t="n">
+        <v>886460400</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1439555000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1439555000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1439555000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>28545000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1468100000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1468100000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>16822000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-1451278000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-30865000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1160695000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>1160695000</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>-143157000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>209951000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>66794000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-117636000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>581403000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>584264000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>401281000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>182983000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>463767000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>16080235000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>16544002000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>16544002000</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU5"/>
+  <dimension ref="A1:BU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1601,834 +1652,917 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>886460400</v>
-      </c>
-      <c r="D2" t="n">
-        <v>886460400</v>
-      </c>
-      <c r="E2" t="n">
-        <v>425162000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3933668000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1321895000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2414855000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-65938000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1321895000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>198775000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1320038000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-1247238000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>91258000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1411296000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1320038000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>25295000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-3223779000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>886460000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>886460000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>10304717000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>177255000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>37742000</v>
+      </c>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>842000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>176413000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>103613000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>72800000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10127462000</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>3757255000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>95162000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3662093000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>6091816000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5138097000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26718000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>927001000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>10395975000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>334451000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>22957000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>22957000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>67821000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>29174000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>38647000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1857000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1857000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>241816000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-693079000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>934895000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>108262000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>826633000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>10061524000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>104885000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>2135073000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>827751000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>386526000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-42304000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>428830000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="n">
-        <v>1585971000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1507121000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-1225249000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>2732370000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>3514197000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>204466000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>3309731000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>3309731000</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>349275000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>886460400</v>
+        <v>732460400</v>
       </c>
       <c r="D3" t="n">
-        <v>886460400</v>
+        <v>732460400</v>
       </c>
       <c r="E3" t="n">
-        <v>3248378000</v>
+        <v>2478450000</v>
       </c>
       <c r="F3" t="n">
-        <v>4180424000</v>
+        <v>2917007000</v>
       </c>
       <c r="G3" t="n">
-        <v>69219000</v>
+        <v>426151000</v>
       </c>
       <c r="H3" t="n">
-        <v>4036256000</v>
+        <v>3131148000</v>
       </c>
       <c r="I3" t="n">
-        <v>-131748000</v>
+        <v>233790000</v>
       </c>
       <c r="J3" t="n">
-        <v>69219000</v>
+        <v>426151000</v>
       </c>
       <c r="K3" t="n">
-        <v>214780000</v>
+        <v>214424000</v>
       </c>
       <c r="L3" t="n">
-        <v>70612000</v>
+        <v>428565000</v>
       </c>
       <c r="M3" t="n">
-        <v>70612000</v>
+        <v>443411000</v>
       </c>
       <c r="N3" t="n">
-        <v>43980000</v>
+        <v>437913000</v>
       </c>
       <c r="O3" t="n">
-        <v>-26632000</v>
+        <v>9348000</v>
       </c>
       <c r="P3" t="n">
-        <v>70612000</v>
+        <v>428565000</v>
       </c>
       <c r="Q3" t="n">
         <v>25295000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1849637000</v>
+        <v>-1219592000</v>
       </c>
       <c r="S3" t="n">
-        <v>886460000</v>
+        <v>732460000</v>
       </c>
       <c r="T3" t="n">
-        <v>886460000</v>
+        <v>732460000</v>
       </c>
       <c r="U3" t="n">
-        <v>8288208000</v>
+        <v>6626578000</v>
       </c>
       <c r="V3" t="n">
-        <v>170993000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>171207000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>21855000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>21855000</v>
+      </c>
       <c r="Y3" t="n">
-        <v>333000</v>
+        <v>605000</v>
       </c>
       <c r="Z3" t="n">
-        <v>170660000</v>
+        <v>148747000</v>
       </c>
       <c r="AA3" t="n">
-        <v>170660000</v>
+        <v>133901000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>14846000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8117215000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-540000</v>
-      </c>
+        <v>6455371000</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>4009764000</v>
+        <v>2768260000</v>
       </c>
       <c r="AF3" t="n">
-        <v>44120000</v>
+        <v>80523000</v>
       </c>
       <c r="AG3" t="n">
-        <v>3965644000</v>
+        <v>2687737000</v>
       </c>
       <c r="AH3" t="n">
-        <v>3697049000</v>
+        <v>3480622000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3255446000</v>
+        <v>3140030000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27996000</v>
+        <v>27541000</v>
       </c>
       <c r="AK3" t="n">
-        <v>413607000</v>
+        <v>313051000</v>
       </c>
       <c r="AL3" t="n">
-        <v>8332188000</v>
+        <v>7064491000</v>
       </c>
       <c r="AM3" t="n">
-        <v>346721000</v>
+        <v>375330000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>20341000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>20000000</v>
+        <v>20341000</v>
       </c>
       <c r="AR3" t="n">
-        <v>69842000</v>
+        <v>102140000</v>
       </c>
       <c r="AS3" t="n">
-        <v>31777000</v>
+        <v>41613000</v>
       </c>
       <c r="AT3" t="n">
-        <v>38065000</v>
+        <v>60527000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1393000</v>
+        <v>2414000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1393000</v>
+        <v>2414000</v>
       </c>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>255486000</v>
+        <v>250435000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-669600000</v>
+        <v>-650490000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>925086000</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>900925000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>250435000</v>
+      </c>
       <c r="BB3" t="n">
-        <v>100759000</v>
+        <v>99144000</v>
       </c>
       <c r="BC3" t="n">
-        <v>824327000</v>
+        <v>801781000</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>7985467000</v>
+        <v>6689161000</v>
       </c>
       <c r="BF3" t="n">
-        <v>86538000</v>
+        <v>89986000</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>179000000</v>
       </c>
       <c r="BH3" t="n">
-        <v>1797640000</v>
+        <v>1043609000</v>
       </c>
       <c r="BI3" t="n">
-        <v>728963000</v>
+        <v>146246000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>331484000</v>
+        <v>275887000</v>
       </c>
       <c r="BK3" t="n">
-        <v>-40623000</v>
+        <v>-66811000</v>
       </c>
       <c r="BL3" t="n">
-        <v>372107000</v>
+        <v>342551000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>147000</v>
       </c>
       <c r="BN3" t="n">
-        <v>1878618000</v>
+        <v>2327772000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2001581000</v>
+        <v>2320591000</v>
       </c>
       <c r="BP3" t="n">
-        <v>-822480000</v>
+        <v>-402433000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2824061000</v>
+        <v>2723024000</v>
       </c>
       <c r="BR3" t="n">
-        <v>1160643000</v>
+        <v>306070000</v>
       </c>
       <c r="BS3" t="n">
-        <v>443377000</v>
+        <v>81937000</v>
       </c>
       <c r="BT3" t="n">
-        <v>717266000</v>
+        <v>224133000</v>
       </c>
       <c r="BU3" t="n">
-        <v>717266000</v>
+        <v>224133000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>732460400</v>
+        <v>886460400</v>
       </c>
       <c r="D4" t="n">
-        <v>732460400</v>
+        <v>886460400</v>
       </c>
       <c r="E4" t="n">
-        <v>2478450000</v>
+        <v>3248378000</v>
       </c>
       <c r="F4" t="n">
-        <v>2917007000</v>
+        <v>4180424000</v>
       </c>
       <c r="G4" t="n">
-        <v>426151000</v>
+        <v>69219000</v>
       </c>
       <c r="H4" t="n">
-        <v>3131148000</v>
+        <v>4036256000</v>
       </c>
       <c r="I4" t="n">
-        <v>233790000</v>
+        <v>-131748000</v>
       </c>
       <c r="J4" t="n">
-        <v>426151000</v>
+        <v>69219000</v>
       </c>
       <c r="K4" t="n">
-        <v>214424000</v>
+        <v>214780000</v>
       </c>
       <c r="L4" t="n">
-        <v>428565000</v>
+        <v>70612000</v>
       </c>
       <c r="M4" t="n">
-        <v>443411000</v>
+        <v>70612000</v>
       </c>
       <c r="N4" t="n">
-        <v>437913000</v>
+        <v>43980000</v>
       </c>
       <c r="O4" t="n">
-        <v>9348000</v>
+        <v>-26632000</v>
       </c>
       <c r="P4" t="n">
-        <v>428565000</v>
+        <v>70612000</v>
       </c>
       <c r="Q4" t="n">
         <v>25295000</v>
       </c>
       <c r="R4" t="n">
-        <v>-1219592000</v>
+        <v>-1849637000</v>
       </c>
       <c r="S4" t="n">
-        <v>732460000</v>
+        <v>886460000</v>
       </c>
       <c r="T4" t="n">
-        <v>732460000</v>
+        <v>886460000</v>
       </c>
       <c r="U4" t="n">
-        <v>6626578000</v>
+        <v>8288208000</v>
       </c>
       <c r="V4" t="n">
-        <v>171207000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>21855000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>21855000</v>
-      </c>
+        <v>170993000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>605000</v>
+        <v>333000</v>
       </c>
       <c r="Z4" t="n">
-        <v>148747000</v>
+        <v>170660000</v>
       </c>
       <c r="AA4" t="n">
-        <v>133901000</v>
+        <v>170660000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14846000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>6455371000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>8117215000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-540000</v>
+      </c>
       <c r="AE4" t="n">
-        <v>2768260000</v>
+        <v>4009764000</v>
       </c>
       <c r="AF4" t="n">
-        <v>80523000</v>
+        <v>44120000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2687737000</v>
+        <v>3965644000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3480622000</v>
+        <v>3697049000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3140030000</v>
+        <v>3255446000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27541000</v>
+        <v>27996000</v>
       </c>
       <c r="AK4" t="n">
-        <v>313051000</v>
+        <v>413607000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7064491000</v>
+        <v>8332188000</v>
       </c>
       <c r="AM4" t="n">
-        <v>375330000</v>
+        <v>346721000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>20341000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>20000000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>20341000</v>
+        <v>20000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>102140000</v>
+        <v>69842000</v>
       </c>
       <c r="AS4" t="n">
-        <v>41613000</v>
+        <v>31777000</v>
       </c>
       <c r="AT4" t="n">
-        <v>60527000</v>
+        <v>38065000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2414000</v>
+        <v>1393000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2414000</v>
+        <v>1393000</v>
       </c>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>250435000</v>
+        <v>255486000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-650490000</v>
+        <v>-669600000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>900925000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>250435000</v>
-      </c>
+        <v>925086000</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>99144000</v>
+        <v>100759000</v>
       </c>
       <c r="BC4" t="n">
-        <v>801781000</v>
+        <v>824327000</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>6689161000</v>
+        <v>7985467000</v>
       </c>
       <c r="BF4" t="n">
-        <v>89986000</v>
+        <v>86538000</v>
       </c>
       <c r="BG4" t="n">
-        <v>179000000</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>1043609000</v>
+        <v>1797640000</v>
       </c>
       <c r="BI4" t="n">
-        <v>146246000</v>
+        <v>728963000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>275887000</v>
+        <v>331484000</v>
       </c>
       <c r="BK4" t="n">
-        <v>-66811000</v>
+        <v>-40623000</v>
       </c>
       <c r="BL4" t="n">
-        <v>342551000</v>
+        <v>372107000</v>
       </c>
       <c r="BM4" t="n">
-        <v>147000</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>2327772000</v>
+        <v>1878618000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2320591000</v>
+        <v>2001581000</v>
       </c>
       <c r="BP4" t="n">
-        <v>-402433000</v>
+        <v>-822480000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2723024000</v>
+        <v>2824061000</v>
       </c>
       <c r="BR4" t="n">
-        <v>306070000</v>
+        <v>1160643000</v>
       </c>
       <c r="BS4" t="n">
-        <v>81937000</v>
+        <v>443377000</v>
       </c>
       <c r="BT4" t="n">
-        <v>224133000</v>
+        <v>717266000</v>
       </c>
       <c r="BU4" t="n">
-        <v>224133000</v>
+        <v>717266000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>732460400</v>
+        <v>886460400</v>
       </c>
       <c r="D5" t="n">
-        <v>732460400</v>
+        <v>886460400</v>
       </c>
       <c r="E5" t="n">
-        <v>2066699000</v>
+        <v>5116162000</v>
       </c>
       <c r="F5" t="n">
-        <v>2455900000</v>
+        <v>8624668000</v>
       </c>
       <c r="G5" t="n">
-        <v>701525000</v>
+        <v>-1321895000</v>
       </c>
       <c r="H5" t="n">
-        <v>2863006000</v>
+        <v>7105855000</v>
       </c>
       <c r="I5" t="n">
-        <v>293703000</v>
+        <v>-65938000</v>
       </c>
       <c r="J5" t="n">
-        <v>701525000</v>
+        <v>-1321895000</v>
       </c>
       <c r="K5" t="n">
-        <v>297976000</v>
+        <v>198775000</v>
       </c>
       <c r="L5" t="n">
-        <v>705082000</v>
+        <v>-1320038000</v>
       </c>
       <c r="M5" t="n">
-        <v>723052000</v>
+        <v>-1247238000</v>
       </c>
       <c r="N5" t="n">
-        <v>717996000</v>
+        <v>91258000</v>
       </c>
       <c r="O5" t="n">
-        <v>12914000</v>
+        <v>1411296000</v>
       </c>
       <c r="P5" t="n">
-        <v>705082000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>-1320038000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>25295000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-3223779000</v>
+      </c>
       <c r="S5" t="n">
-        <v>732460000</v>
+        <v>886460000</v>
       </c>
       <c r="T5" t="n">
-        <v>732460000</v>
+        <v>886460000</v>
       </c>
       <c r="U5" t="n">
-        <v>6656738000</v>
+        <v>10304717000</v>
       </c>
       <c r="V5" t="n">
-        <v>240034000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>37742000</v>
-      </c>
+        <v>177255000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>1700000</v>
+        <v>842000</v>
       </c>
       <c r="Z5" t="n">
-        <v>200592000</v>
+        <v>176413000</v>
       </c>
       <c r="AA5" t="n">
-        <v>182622000</v>
+        <v>103613000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17970000</v>
+        <v>72800000</v>
       </c>
       <c r="AC5" t="n">
-        <v>6416704000</v>
+        <v>10127462000</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>2255308000</v>
+        <v>8448255000</v>
       </c>
       <c r="AF5" t="n">
-        <v>115354000</v>
+        <v>95162000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2139954000</v>
+        <v>8353093000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3908839000</v>
+        <v>1400720000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3181015000</v>
+        <v>447001000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8630000</v>
+        <v>26718000</v>
       </c>
       <c r="AK5" t="n">
-        <v>719194000</v>
+        <v>927001000</v>
       </c>
       <c r="AL5" t="n">
-        <v>7374734000</v>
+        <v>10395975000</v>
       </c>
       <c r="AM5" t="n">
-        <v>664327000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
+        <v>334451000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1509000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>500000</v>
-      </c>
+        <v>22957000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>1009000</v>
+        <v>22957000</v>
       </c>
       <c r="AR5" t="n">
-        <v>309986000</v>
+        <v>67821000</v>
       </c>
       <c r="AS5" t="n">
-        <v>54531000</v>
+        <v>29174000</v>
       </c>
       <c r="AT5" t="n">
-        <v>255455000</v>
+        <v>38647000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3557000</v>
+        <v>1857000</v>
       </c>
       <c r="AV5" t="n">
-        <v>3557000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
+        <v>1857000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>349275000</v>
+        <v>241816000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-628489000</v>
+        <v>-693079000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>977764000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>349275000</v>
-      </c>
+        <v>934895000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>97275000</v>
+        <v>108262000</v>
       </c>
       <c r="BC5" t="n">
-        <v>880489000</v>
+        <v>826633000</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>6710407000</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
+        <v>10061524000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>104885000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>729355000</v>
+        <v>2135073000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2167047000</v>
+        <v>827748000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>294308000</v>
+        <v>386526000</v>
       </c>
       <c r="BK5" t="n">
-        <v>-46237000</v>
+        <v>-42304000</v>
       </c>
       <c r="BL5" t="n">
-        <v>339095000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1450000</v>
-      </c>
+        <v>428830000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>432453000</v>
+        <v>743463000</v>
       </c>
       <c r="BO5" t="n">
-        <v>2891620000</v>
+        <v>2349632000</v>
       </c>
       <c r="BP5" t="n">
-        <v>-245609000</v>
+        <v>-1234190000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3137229000</v>
+        <v>3583822000</v>
       </c>
       <c r="BR5" t="n">
-        <v>195624000</v>
+        <v>3514197000</v>
       </c>
       <c r="BS5" t="n">
-        <v>104399000</v>
+        <v>204466000</v>
       </c>
       <c r="BT5" t="n">
-        <v>91225000</v>
+        <v>3309731000</v>
       </c>
       <c r="BU5" t="n">
-        <v>91225000</v>
+        <v>3309731000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>886460400</v>
+      </c>
+      <c r="D6" t="n">
+        <v>886460400</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5269044000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7270023000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2757764000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4356878000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-1457052000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-2757764000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>156754000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2756391000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-2631591000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1374450000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1381941000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2756391000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>25295000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-4706558000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>886460000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>886460000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8734590000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>216796000</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>1403000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>215393000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>90593000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>124800000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>8517794000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>7054630000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>66161000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6988469000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>926259000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>683593000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>32250000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>210416000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7360140000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>299398000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>25383000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>25383000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>70281000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>34980000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>35301000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1373000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1373000</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>202361000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-719450000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>921811000</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>106771000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>815040000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>7060742000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>84563000</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>2349454000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>865164000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>481179000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-43166000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>524345000</v>
+      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="n">
+        <v>528967000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>886190000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-1848583000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2734773000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1865225000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1844225000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1844225000</v>
       </c>
     </row>
   </sheetData>
@@ -2442,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA5"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2709,504 +2843,434 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-154579000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-11837889000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>13542336000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>-22211000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3309731000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>717266000</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>2592465000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2501265000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1112835000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-191038000</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>-2881000</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>1704447000</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>-4057330000</v>
+        <v>1723454000</v>
       </c>
       <c r="R2" t="n">
-        <v>-4057330000</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>5761777000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-7780559000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>13542336000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>223568000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1109000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>701000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>243969000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1723454000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>991000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>39792000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-977000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-977000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-21234000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>-21234000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-132368000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-3539000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-437610000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-82565000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>434288000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-65787000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-56723000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-666823000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>172799000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>734324000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>143487000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>513000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>142974000</v>
-      </c>
+        <v>39792000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-1918000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-3146000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>948000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-12930000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-1404183000</v>
-      </c>
+        <v>-3219000</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>39217000</v>
+        <v>-612181000</v>
       </c>
       <c r="C3" t="n">
-        <v>-8938412000</v>
+        <v>-8472693000</v>
       </c>
       <c r="D3" t="n">
-        <v>10404784000</v>
+        <v>9799787000</v>
       </c>
       <c r="E3" t="n">
-        <v>238664000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-18306000</v>
+        <v>-12692000</v>
       </c>
       <c r="G3" t="n">
-        <v>717266000</v>
+        <v>224133000</v>
       </c>
       <c r="H3" t="n">
-        <v>224133000</v>
+        <v>91225000</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>629000</v>
       </c>
       <c r="J3" t="n">
-        <v>493133000</v>
+        <v>132279000</v>
       </c>
       <c r="K3" t="n">
-        <v>613932000</v>
+        <v>721443000</v>
       </c>
       <c r="L3" t="n">
-        <v>-782291000</v>
+        <v>-313384000</v>
       </c>
       <c r="M3" t="n">
-        <v>-168420000</v>
+        <v>-165088000</v>
       </c>
       <c r="N3" t="n">
-        <v>238664000</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>238664000</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1466372000</v>
+        <v>1327094000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3106426000</v>
+        <v>780531000</v>
       </c>
       <c r="R3" t="n">
-        <v>-3106426000</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>-3661529000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4442060000</v>
+      </c>
       <c r="T3" t="n">
-        <v>4572798000</v>
+        <v>1327094000</v>
       </c>
       <c r="U3" t="n">
-        <v>-5831986000</v>
+        <v>-8472693000</v>
       </c>
       <c r="V3" t="n">
-        <v>10404784000</v>
+        <v>9799787000</v>
       </c>
       <c r="W3" t="n">
-        <v>-178322000</v>
+        <v>10325000</v>
       </c>
       <c r="X3" t="n">
-        <v>21000</v>
+        <v>101000</v>
       </c>
       <c r="Y3" t="n">
-        <v>564000</v>
+        <v>481000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-354101000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>22435000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22435000</v>
+      </c>
       <c r="AB3" t="n">
-        <v>193500000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>193500000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-89000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>-18217000</v>
+        <v>-12692000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-18217000</v>
+        <v>-12692000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>57523000</v>
+        <v>-599489000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-4762000</v>
+        <v>-852000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-296159000</v>
+        <v>-796384000</v>
       </c>
       <c r="AM3" t="n">
-        <v>267195000</v>
+        <v>-41199000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-38736000</v>
+        <v>-1255345000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-228591000</v>
+        <v>291902000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-29408000</v>
+        <v>-2154000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-266619000</v>
+        <v>210412000</v>
       </c>
       <c r="AR3" t="n">
-        <v>179806000</v>
+        <v>176629000</v>
       </c>
       <c r="AS3" t="n">
-        <v>420047000</v>
+        <v>157332000</v>
       </c>
       <c r="AT3" t="n">
-        <v>143970000</v>
+        <v>139584000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1110000</v>
+        <v>1143000</v>
       </c>
       <c r="AV3" t="n">
-        <v>142860000</v>
+        <v>138441000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-7439000</v>
+        <v>528000</v>
       </c>
       <c r="AX3" t="n">
-        <v>5107000</v>
+        <v>1857000</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>5978000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2923000</v>
+        <v>-1468000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-661080000</v>
+        <v>-260477000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-612181000</v>
+        <v>39217000</v>
       </c>
       <c r="C4" t="n">
-        <v>-8472693000</v>
+        <v>-8938412000</v>
       </c>
       <c r="D4" t="n">
-        <v>9799787000</v>
+        <v>10404784000</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>238664000</v>
       </c>
       <c r="F4" t="n">
-        <v>-12692000</v>
+        <v>-18306000</v>
       </c>
       <c r="G4" t="n">
+        <v>717266000</v>
+      </c>
+      <c r="H4" t="n">
         <v>224133000</v>
       </c>
-      <c r="H4" t="n">
-        <v>91225000</v>
-      </c>
       <c r="I4" t="n">
-        <v>629000</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>132279000</v>
+        <v>493133000</v>
       </c>
       <c r="K4" t="n">
-        <v>721443000</v>
+        <v>613932000</v>
       </c>
       <c r="L4" t="n">
-        <v>-313384000</v>
+        <v>-782291000</v>
       </c>
       <c r="M4" t="n">
-        <v>-165088000</v>
+        <v>-168420000</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>238664000</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>238664000</v>
       </c>
       <c r="P4" t="n">
-        <v>1327094000</v>
+        <v>1466372000</v>
       </c>
       <c r="Q4" t="n">
-        <v>780531000</v>
+        <v>-3106426000</v>
       </c>
       <c r="R4" t="n">
-        <v>-3661529000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4442060000</v>
-      </c>
+        <v>-3106426000</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>1327094000</v>
+        <v>4572798000</v>
       </c>
       <c r="U4" t="n">
-        <v>-8472693000</v>
+        <v>-5831986000</v>
       </c>
       <c r="V4" t="n">
-        <v>9799787000</v>
+        <v>10404784000</v>
       </c>
       <c r="W4" t="n">
-        <v>10325000</v>
+        <v>-178322000</v>
       </c>
       <c r="X4" t="n">
-        <v>101000</v>
+        <v>21000</v>
       </c>
       <c r="Y4" t="n">
-        <v>481000</v>
+        <v>564000</v>
       </c>
       <c r="Z4" t="n">
-        <v>22435000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>22435000</v>
-      </c>
+        <v>-354101000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>193500000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>193500000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-89000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-89000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-12692000</v>
+        <v>-18217000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-12692000</v>
+        <v>-18217000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-599489000</v>
+        <v>57523000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-852000</v>
+        <v>-4762000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-796384000</v>
+        <v>-296159000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-41199000</v>
+        <v>267195000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1255345000</v>
+        <v>-38736000</v>
       </c>
       <c r="AO4" t="n">
-        <v>291902000</v>
+        <v>-228591000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2154000</v>
+        <v>-29408000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>210412000</v>
+        <v>-266619000</v>
       </c>
       <c r="AR4" t="n">
-        <v>176629000</v>
+        <v>179806000</v>
       </c>
       <c r="AS4" t="n">
-        <v>157332000</v>
+        <v>420047000</v>
       </c>
       <c r="AT4" t="n">
-        <v>139584000</v>
+        <v>143970000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1143000</v>
+        <v>1110000</v>
       </c>
       <c r="AV4" t="n">
-        <v>138441000</v>
+        <v>142860000</v>
       </c>
       <c r="AW4" t="n">
-        <v>528000</v>
+        <v>-7439000</v>
       </c>
       <c r="AX4" t="n">
-        <v>1857000</v>
+        <v>5107000</v>
       </c>
       <c r="AY4" t="n">
-        <v>5978000</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1468000</v>
+        <v>2923000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-260477000</v>
+        <v>-661080000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1011458000</v>
+        <v>-154579000</v>
       </c>
       <c r="C5" t="n">
-        <v>-5947533000</v>
+        <v>-11837889000</v>
       </c>
       <c r="D5" t="n">
-        <v>7006659000</v>
+        <v>13542336000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-18835000</v>
+        <v>-22211000</v>
       </c>
       <c r="G5" t="n">
-        <v>91225000</v>
+        <v>3309731000</v>
       </c>
       <c r="H5" t="n">
-        <v>71413000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2881000</v>
-      </c>
+        <v>717266000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>22693000</v>
+        <v>2592465000</v>
       </c>
       <c r="K5" t="n">
-        <v>1045794000</v>
+        <v>2501265000</v>
       </c>
       <c r="L5" t="n">
-        <v>359985000</v>
+        <v>1112835000</v>
       </c>
       <c r="M5" t="n">
-        <v>-209694000</v>
+        <v>-191038000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -3215,118 +3279,249 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1059126000</v>
+        <v>1704447000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1723454000</v>
+        <v>-4057330000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1723454000</v>
-      </c>
+        <v>-4057330000</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-664328000</v>
+        <v>1704447000</v>
       </c>
       <c r="U5" t="n">
-        <v>-5947533000</v>
+        <v>-11837889000</v>
       </c>
       <c r="V5" t="n">
-        <v>5283205000</v>
+        <v>13542336000</v>
       </c>
       <c r="W5" t="n">
-        <v>-30478000</v>
+        <v>223568000</v>
       </c>
       <c r="X5" t="n">
-        <v>3000</v>
+        <v>1109000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>701000</v>
       </c>
       <c r="Z5" t="n">
-        <v>991000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>991000</v>
-      </c>
+        <v>243969000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>39792000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>39792000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-977000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-977000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-18835000</v>
+        <v>-21234000</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-18835000</v>
+        <v>-21234000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-992623000</v>
+        <v>-132368000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-21383000</v>
+        <v>-3539000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-437747000</v>
+        <v>-437610000</v>
       </c>
       <c r="AM5" t="n">
-        <v>40273000</v>
+        <v>-82478000</v>
       </c>
       <c r="AN5" t="n">
-        <v>544097000</v>
+        <v>434201000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-683684000</v>
+        <v>-70256000</v>
       </c>
       <c r="AP5" t="n">
-        <v>337661000</v>
+        <v>-56723000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-676094000</v>
+        <v>-662354000</v>
       </c>
       <c r="AR5" t="n">
-        <v>232088000</v>
+        <v>172799000</v>
       </c>
       <c r="AS5" t="n">
-        <v>3008000</v>
+        <v>739159000</v>
       </c>
       <c r="AT5" t="n">
-        <v>184996000</v>
+        <v>143487000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1377000</v>
+        <v>513000</v>
       </c>
       <c r="AV5" t="n">
-        <v>183619000</v>
+        <v>142974000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-3219000</v>
+        <v>-1918000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-1704000</v>
+        <v>-3146000</v>
       </c>
       <c r="AY5" t="n">
-        <v>7950000</v>
+        <v>948000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-12930000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-3905349000</v>
+        <v>-1404183000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>211938000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-9239184000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7926560000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>-24268000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1844225000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3309731000</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>-1465506000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1863371000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-240443000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-184357000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>-1312624000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>-1312624000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-9239184000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7926560000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>161659000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2183000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>183466000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-209000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-209000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-23781000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>278000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-24059000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>236206000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-10225000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>181507000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>226741000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-657250000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>155834000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-99840000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>556022000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>207768000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>856479000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>134047000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>693000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>133354000</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>179000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>9401000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-1451278000</v>
       </c>
     </row>
   </sheetData>
@@ -3821,192 +4016,192 @@
       </c>
       <c r="CR1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
@@ -4078,7 +4273,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Beijing Digital Telecom Co., Ltd., together with its subsidiaries, engages in the sale of mobile telecommunications devices and accessories, and provision of related services in Mainland China. It operates through two segments, Traditional Based Operation - Mobile Related and New Developed Operation - Others. The company is involved in the sale of mobile telecommunications devices and accessories through independently operated outlets and store-in-store outlets, stores in cooperation with the mobile carriers, and online sales platforms, as well as sales to its franchisees. It also engages in the wholesale of mobile telecommunications devices and accessories to mobile carriers and other third-party retailers. In addition, the company provides management services to suppliers of products; value-added services for software; repair and maintenance services; and personalized and after-sales services for mobile phones, as well as rents counter space to third parties that offer repair services. Further, it sells vehicles, photovoltaic equipment, and other products; and sells mobile phone hardware and accessories. Beijing Digital Telecom Co., Ltd. was founded in 1993 and is headquartered in Beijing, the People's Republic of China.</t>
+          <t>Beijing Digital Telecom Co., Ltd., together with its subsidiaries, engages in the sale of mobile telecommunications devices and accessories, and provision of related services in Mainland China. It operates through two segments, Traditional Based Operation - Mobile Related and New Developed Operation - Others. The company is involved in the sale of mobile telecommunications devices and accessories through independently operated outlets and store-in-store outlets, stores in cooperation with the mobile carriers, and online sales platforms, as well as sales to its franchisees. It also engages in the wholesale of mobile telecommunications devices and accessories to mobile carriers and other third-party retailers. In addition, the company provides management services to suppliers of products; value-added services for software; repair and maintenance services; and after-sales services for mobile phones, as well as rents counter space to third parties that offer repair services. Further, it sells vehicles, photovoltaic equipment, and other products; and sells mobile phone hardware and accessories. Beijing Digital Telecom Co., Ltd. was founded in 1993 and is headquartered in Beijing, the People's Republic of China.</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -4086,7 +4281,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Jili  Xu', 'age': 53, 'title': 'Chairwoman &amp; President', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Liu', 'age': 45, 'title': 'President &amp; Executive Director', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Donghai  Liu', 'age': 59, 'title': 'Founder &amp; Executive Director', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 236586, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Liping  Xu', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guohui  DU', 'age': 46, 'title': 'General Manager', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Fengjuan  Su', 'age': 42, 'title': 'Chief Financial Officer', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  Qi', 'age': 56, 'title': 'Vice General Manager', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qing  Zhou', 'age': 57, 'title': 'Vice General Manager', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianhui  Huang', 'age': 65, 'title': 'Vice General Manager', 'yearBorn': 1960, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mingqiang  Huang', 'age': 40, 'title': 'Joint Company Secretary &amp; Board Secretary', 'yearBorn': 1985, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Jili  Xu', 'age': 53, 'title': 'Chairwoman &amp; President', 'yearBorn': 1972, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Liu', 'age': 45, 'title': 'President &amp; Executive Director', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Donghai  Liu', 'age': 59, 'title': 'Founder &amp; Executive Director', 'yearBorn': 1966, 'fiscalYear': 2025, 'totalPay': 237512, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Liping  Xu', 'age': 43, 'title': 'Executive Director', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guohui  DU', 'age': 46, 'title': 'General Manager', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Fengjuan  Su', 'age': 42, 'title': 'Chief Financial Officer', 'yearBorn': 1983, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Feng  Qi', 'age': 56, 'title': 'Vice General Manager', 'yearBorn': 1969, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Qing  Zhou', 'age': 57, 'title': 'Vice General Manager', 'yearBorn': 1968, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianhui  Huang', 'age': 65, 'title': 'Vice General Manager', 'yearBorn': 1960, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mingqiang  Huang', 'age': 40, 'title': 'Joint Company Secretary &amp; Board Secretary', 'yearBorn': 1985, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4104,43 +4299,43 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0675</v>
+        <v>0.067</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0675</v>
+        <v>0.067</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0675</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0675</v>
+        <v>0.067</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0675</v>
+        <v>0.067</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0675</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.897</v>
       </c>
       <c r="AD2" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AE2" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -4149,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.0635</v>
+        <v>0.06</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AK2" t="n">
         <v>14600</v>
@@ -4161,10 +4356,10 @@
         <v>14600</v>
       </c>
       <c r="AM2" t="n">
-        <v>59836080</v>
+        <v>62052228</v>
       </c>
       <c r="AN2" t="n">
-        <v>65066610</v>
+        <v>67840742</v>
       </c>
       <c r="AO2" t="n">
         <v>0.0175</v>
@@ -4179,13 +4374,13 @@
         <v>0.0175</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.003616784</v>
+        <v>0.0037507387</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.04021</v>
+        <v>0.0463</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.046445</v>
+        <v>0.04562</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4202,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6767159296</v>
+        <v>6764942848</v>
       </c>
       <c r="BA2" t="n">
         <v>-0.08701</v>
@@ -4223,7 +4418,7 @@
         <v>886460400</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.39403278</v>
+        <v>-0.3965759</v>
       </c>
       <c r="BH2" t="n">
         <v>1767139200</v>
@@ -4244,13 +4439,13 @@
         <v>0.409</v>
       </c>
       <c r="BN2" t="n">
-        <v>-6.813</v>
+        <v>-6.81</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.3166666</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -4258,7 +4453,7 @@
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>0.0675</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -4351,143 +4546,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>1412920800000</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.0029999986</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>0.067 - 0.07</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.052500002</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>0.0175 - 0.147</t>
+        </is>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.077</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.5238095</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1743026601</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1743026601</v>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>4.4776096</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1781852351</v>
+      </c>
+      <c r="DK2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>finmb_28385605</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="CV2" t="n">
+      <c r="DO2" t="n">
         <v>7200000</v>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>dr_market</t>
         </is>
       </c>
-      <c r="CX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>-2.8776932</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>1780380716</v>
-      </c>
-      <c r="DC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>1412920800000</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.0019999966</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>0.0675 - 0.0675</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.050000004</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.8571432</v>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.023699999</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.511879</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.024379998</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.53441465</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.17651097</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Beijing Digital Telekom Co.LtdR</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Beijing Digital Telecom Co., Ltd.</t>
         </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Beijing Digital Telekom Co.LtdR</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.027290002</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.6786869</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.021055002</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.45333192</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>-0.17130555</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>0.0175 - 0.147</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.0795</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.5408163</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>131.66666</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1743026601</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1743026601</v>
       </c>
       <c r="ED2" t="inlineStr"/>
     </row>
